--- a/nr-fix-issue24-anchor-x-links/ig/FRObservationPregnancyLMCDAFHIR.xlsx
+++ b/nr-fix-issue24-anchor-x-links/ig/FRObservationPregnancyLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T09:22:48+00:00</t>
+    <t>2026-09-15T09:43:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-fix-issue24-anchor-x-links/ig/FRObservationPregnancyLMCDAFHIR.xlsx
+++ b/nr-fix-issue24-anchor-x-links/ig/FRObservationPregnancyLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T09:43:37+00:00</t>
+    <t>2026-09-15T10:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-fix-issue24-anchor-x-links/ig/FRObservationPregnancyLMCDAFHIR.xlsx
+++ b/nr-fix-issue24-anchor-x-links/ig/FRObservationPregnancyLMCDAFHIR.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T10:02:45+00:00</t>
+    <t>2026-09-15T11:02:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
